--- a/exports/bunds/bunds_curveTradesRecap_hitRate.xlsx
+++ b/exports/bunds/bunds_curveTradesRecap_hitRate.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccardo/Desktop/Personal Projects/Latest/Yield curve models/gauss+/exports/bunds/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB869DC-FBBC-2646-9703-7CE4639B9376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="9340" yWindow="800" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="output" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>frontend</t>
   </si>
@@ -33,12 +39,15 @@
   <si>
     <t>Source: BSIC</t>
   </si>
+  <si>
+    <t>German Bunds, average hit rates</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -183,6 +192,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -191,13 +203,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +255,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -269,6 +289,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -303,9 +324,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -478,94 +500,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:F8"/>
-  <sheetFormatPr defaultRowHeight="15.5" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="6" width="9.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.5" customHeight="1">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="15.5" customHeight="1">
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
-        <v>0.4588</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.3803</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.4456</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="15.5" customHeight="1">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.4245</v>
+        <v>0.45879999999999999</v>
       </c>
       <c r="E4" s="4">
-        <v>0.5291</v>
+        <v>0.38030000000000003</v>
       </c>
       <c r="F4" s="5">
-        <v>0.6056</v>
+        <v>0.4456</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.5" customHeight="1">
+    <row r="5" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.42449999999999999</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.52910000000000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.60560000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>0.6142</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.6689000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="15.5" customHeight="1">
-      <c r="B6" s="6" t="s">
-        <v>3</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0.61419999999999997</v>
+      </c>
       <c r="F6" s="5">
+        <v>0.66890000000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="5" customHeight="1"/>
-    <row r="8" spans="2:6" ht="15.5" customHeight="1">
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="2:6" ht="5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:F8"/>
+  <mergeCells count="2">
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
